--- a/Documentation/Best For Weighting Tables/Best for Seniors with Dementia.xlsx
+++ b/Documentation/Best For Weighting Tables/Best for Seniors with Dementia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B7351F0-8D06-4039-AA5F-FC74FDF7C614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD98EABC-9DB0-4E3B-B185-DBB33DB207BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{A4FB888C-FD96-4C4B-A1F5-34A522709FD3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FB888C-FD96-4C4B-A1F5-34A522709FD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Best for Seniors with Dementia" sheetId="1" r:id="rId1"/>
@@ -56,9 +56,6 @@
     <t>Emotional comfort potential</t>
   </si>
   <si>
-    <t>Noise sensitivity fit</t>
-  </si>
-  <si>
     <t>Recognizable pet appearance</t>
   </si>
   <si>
@@ -66,6 +63,9 @@
   </si>
   <si>
     <t>Simplicity of use</t>
+  </si>
+  <si>
+    <t>Sound quality</t>
   </si>
 </sst>
 </file>
@@ -495,7 +495,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3">
         <v>0.1</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
@@ -511,7 +511,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
         <v>0.2</v>
